--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N39_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>53.45431566413831</v>
       </c>
       <c r="E2" t="n">
-        <v>19.1022981638689</v>
+        <v>18.6353224374351</v>
       </c>
       <c r="F2" t="n">
-        <v>15.74156145767754</v>
+        <v>17.46431994358059</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>16.29855591797836</v>
       </c>
       <c r="E3" t="n">
-        <v>19.1022981638689</v>
+        <v>18.6353224374351</v>
       </c>
       <c r="F3" t="n">
-        <v>15.74156145767754</v>
+        <v>17.46431994358059</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,23 +544,55 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
+        <v>9.256838708270415</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.692136965687465</v>
+      </c>
+      <c r="E4" t="n">
+        <v>18.6353224374351</v>
+      </c>
+      <c r="F4" t="n">
+        <v>17.46431994358059</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>T7604</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>W0029F0003T0006Z000C1N39.png</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
         <v>13.88767297034076</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>25.95048792371642</v>
       </c>
-      <c r="E4" t="n">
-        <v>19.1022981638689</v>
-      </c>
-      <c r="F4" t="n">
-        <v>15.74156145767754</v>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="E5" t="n">
+        <v>18.6353224374351</v>
+      </c>
+      <c r="F5" t="n">
+        <v>17.46431994358059</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>T7604</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.01196328571465</v>
+        <v>9.10194403392863</v>
       </c>
       <c r="D2" t="n">
-        <v>53.45431566413831</v>
+        <v>8.686326295422475</v>
       </c>
       <c r="E2" t="n">
-        <v>18.6353224374351</v>
+        <v>3.028239896083203</v>
       </c>
       <c r="F2" t="n">
-        <v>17.46431994358059</v>
+        <v>2.837951990831846</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.30900742654224</v>
+        <v>2.812713706813114</v>
       </c>
       <c r="D3" t="n">
-        <v>16.29855591797836</v>
+        <v>2.648515336671483</v>
       </c>
       <c r="E3" t="n">
-        <v>18.6353224374351</v>
+        <v>3.028239896083203</v>
       </c>
       <c r="F3" t="n">
-        <v>17.46431994358059</v>
+        <v>2.837951990831846</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.256838708270415</v>
+        <v>1.504236290093943</v>
       </c>
       <c r="D4" t="n">
-        <v>6.692136965687465</v>
+        <v>1.087472256924213</v>
       </c>
       <c r="E4" t="n">
-        <v>18.6353224374351</v>
+        <v>3.028239896083203</v>
       </c>
       <c r="F4" t="n">
-        <v>17.46431994358059</v>
+        <v>2.837951990831846</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.88767297034076</v>
+        <v>2.256746857680374</v>
       </c>
       <c r="D5" t="n">
-        <v>25.95048792371642</v>
+        <v>4.216954287603918</v>
       </c>
       <c r="E5" t="n">
-        <v>18.6353224374351</v>
+        <v>3.028239896083203</v>
       </c>
       <c r="F5" t="n">
-        <v>17.46431994358059</v>
+        <v>2.837951990831846</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
